--- a/livrables/synthese_troncon.xlsx
+++ b/livrables/synthese_troncon.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="synthese_troncon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'synthese_troncon'!$A$1:$AC$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'synthese_troncon'!$A$1:$AC$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -640,61 +640,61 @@
         <v>3.832</v>
       </c>
       <c r="I2" t="n">
-        <v>269.24</v>
+        <v>269.55</v>
       </c>
       <c r="J2" t="n">
-        <v>7.97</v>
+        <v>13.93</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>3.12</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>106.2</v>
+        <v>97.77</v>
       </c>
       <c r="O2" t="n">
-        <v>39.4</v>
+        <v>36.3</v>
       </c>
       <c r="P2" t="n">
-        <v>57.09</v>
+        <v>67.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.2</v>
+        <v>25.2</v>
       </c>
       <c r="R2" t="n">
-        <v>81.05</v>
+        <v>73.92</v>
       </c>
       <c r="S2" t="n">
-        <v>30.1</v>
+        <v>27.4</v>
       </c>
       <c r="T2" t="n">
-        <v>13.81</v>
+        <v>14.08</v>
       </c>
       <c r="U2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="V2" t="n">
-        <v>117.29</v>
+        <v>113.6</v>
       </c>
       <c r="W2" t="n">
-        <v>43.6</v>
+        <v>42.1</v>
       </c>
       <c r="X2" t="n">
-        <v>65.3</v>
+        <v>66.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>30.1</v>
+        <v>26.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>164.7</v>
+        <v>167.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>102.3</v>
+        <v>104</v>
       </c>
       <c r="AB2" t="n">
         <v>199.1</v>
@@ -735,61 +735,61 @@
         <v>4.824</v>
       </c>
       <c r="I3" t="n">
-        <v>269.24</v>
+        <v>269.55</v>
       </c>
       <c r="J3" t="n">
-        <v>72.92</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>27.1</v>
+        <v>31.1</v>
       </c>
       <c r="L3" t="n">
-        <v>72.53</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>26.9</v>
+        <v>24.6</v>
       </c>
       <c r="N3" t="n">
-        <v>36.43</v>
+        <v>38.52</v>
       </c>
       <c r="O3" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="P3" t="n">
-        <v>38.58</v>
+        <v>34.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
-        <v>44.85</v>
+        <v>42.55</v>
       </c>
       <c r="S3" t="n">
-        <v>16.7</v>
+        <v>15.8</v>
       </c>
       <c r="T3" t="n">
-        <v>3.93</v>
+        <v>3.44</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>181.88</v>
+        <v>188.57</v>
       </c>
       <c r="W3" t="n">
-        <v>67.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="X3" t="n">
-        <v>86.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>61.2</v>
+        <v>56.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>207.2</v>
+        <v>210.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>128.7</v>
+        <v>130.7</v>
       </c>
       <c r="AB3" t="n">
         <v>250.7</v>
@@ -830,37 +830,37 @@
         <v>5.755</v>
       </c>
       <c r="I4" t="n">
-        <v>269.24</v>
+        <v>269.55</v>
       </c>
       <c r="J4" t="n">
-        <v>119.54</v>
+        <v>115.85</v>
       </c>
       <c r="K4" t="n">
-        <v>44.4</v>
+        <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>34.74</v>
+        <v>42.89</v>
       </c>
       <c r="M4" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="N4" t="n">
-        <v>39.04</v>
+        <v>42.14</v>
       </c>
       <c r="O4" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="P4" t="n">
-        <v>57.59</v>
+        <v>49.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.4</v>
+        <v>18.3</v>
       </c>
       <c r="R4" t="n">
-        <v>18.33</v>
+        <v>19.21</v>
       </c>
       <c r="S4" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -869,22 +869,22 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>193.32</v>
+        <v>200.88</v>
       </c>
       <c r="W4" t="n">
-        <v>71.8</v>
+        <v>74.5</v>
       </c>
       <c r="X4" t="n">
-        <v>91.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>246</v>
+        <v>249.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="AB4" t="n">
         <v>299.1</v>
@@ -925,67 +925,67 @@
         <v>3.832</v>
       </c>
       <c r="I5" t="n">
-        <v>184.49</v>
+        <v>184.8</v>
       </c>
       <c r="J5" t="n">
-        <v>52.8</v>
+        <v>14.01</v>
       </c>
       <c r="K5" t="n">
-        <v>28.6</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
-        <v>24.1</v>
+        <v>13.1</v>
       </c>
       <c r="M5" t="n">
-        <v>13.1</v>
+        <v>7.1</v>
       </c>
       <c r="N5" t="n">
-        <v>27.64</v>
+        <v>37.84</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>20.5</v>
       </c>
       <c r="P5" t="n">
-        <v>23.91</v>
+        <v>20.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>11.2</v>
       </c>
       <c r="R5" t="n">
-        <v>50.24</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>27.2</v>
+        <v>51.6</v>
       </c>
       <c r="T5" t="n">
-        <v>5.8</v>
+        <v>3.88</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>104.54</v>
+        <v>64.95</v>
       </c>
       <c r="W5" t="n">
-        <v>56.7</v>
+        <v>35.1</v>
       </c>
       <c r="X5" t="n">
-        <v>68.8</v>
+        <v>43.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>48.7</v>
+        <v>49.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>187.4</v>
+        <v>157.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>116.4</v>
+        <v>98</v>
       </c>
       <c r="AB5" t="n">
-        <v>237.2</v>
+        <v>130.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>147.4</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -1020,67 +1020,67 @@
         <v>4.824</v>
       </c>
       <c r="I6" t="n">
-        <v>184.49</v>
+        <v>184.8</v>
       </c>
       <c r="J6" t="n">
-        <v>92.14</v>
+        <v>54.33</v>
       </c>
       <c r="K6" t="n">
-        <v>49.9</v>
+        <v>29.4</v>
       </c>
       <c r="L6" t="n">
-        <v>24.26</v>
+        <v>22.12</v>
       </c>
       <c r="M6" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>15.81</v>
+        <v>11.21</v>
       </c>
       <c r="O6" t="n">
-        <v>8.6</v>
+        <v>6.1</v>
       </c>
       <c r="P6" t="n">
-        <v>30.82</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.7</v>
+        <v>42.1</v>
       </c>
       <c r="R6" t="n">
-        <v>20.08</v>
+        <v>19.29</v>
       </c>
       <c r="S6" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>132.21</v>
+        <v>87.66</v>
       </c>
       <c r="W6" t="n">
-        <v>71.7</v>
+        <v>47.4</v>
       </c>
       <c r="X6" t="n">
-        <v>88.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>69.5</v>
+        <v>68.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>232.1</v>
+        <v>197.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>144.2</v>
+        <v>122.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>298.6</v>
+        <v>164.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>185.5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -1115,37 +1115,37 @@
         <v>5.755</v>
       </c>
       <c r="I7" t="n">
-        <v>184.49</v>
+        <v>184.8</v>
       </c>
       <c r="J7" t="n">
-        <v>104.56</v>
+        <v>64.97</v>
       </c>
       <c r="K7" t="n">
-        <v>56.7</v>
+        <v>35.2</v>
       </c>
       <c r="L7" t="n">
-        <v>20.91</v>
+        <v>17.51</v>
       </c>
       <c r="M7" t="n">
-        <v>11.3</v>
+        <v>9.5</v>
       </c>
       <c r="N7" t="n">
-        <v>8.890000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="P7" t="n">
-        <v>39.98</v>
+        <v>83.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.7</v>
+        <v>45.3</v>
       </c>
       <c r="R7" t="n">
-        <v>10.15</v>
+        <v>9.02</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1154,28 +1154,28 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>134.36</v>
+        <v>92.09</v>
       </c>
       <c r="W7" t="n">
-        <v>72.8</v>
+        <v>49.8</v>
       </c>
       <c r="X7" t="n">
-        <v>93</v>
+        <v>92.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>72.7</v>
+        <v>75.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>266.1</v>
+        <v>233.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>165.3</v>
+        <v>144.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>356.2</v>
+        <v>195.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>221.3</v>
+        <v>121.7</v>
       </c>
     </row>
     <row r="8">
@@ -1210,67 +1210,67 @@
         <v>3.832</v>
       </c>
       <c r="I8" t="n">
-        <v>441.83</v>
+        <v>442.56</v>
       </c>
       <c r="J8" t="n">
-        <v>58.56</v>
+        <v>49.79</v>
       </c>
       <c r="K8" t="n">
-        <v>13.3</v>
+        <v>11.3</v>
       </c>
       <c r="L8" t="n">
-        <v>50.25</v>
+        <v>51.04</v>
       </c>
       <c r="M8" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="N8" t="n">
-        <v>131.47</v>
+        <v>128.1</v>
       </c>
       <c r="O8" t="n">
-        <v>29.8</v>
+        <v>28.9</v>
       </c>
       <c r="P8" t="n">
-        <v>106.79</v>
+        <v>115.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.2</v>
+        <v>26</v>
       </c>
       <c r="R8" t="n">
-        <v>83.31999999999999</v>
+        <v>93.22</v>
       </c>
       <c r="S8" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="T8" t="n">
-        <v>11.44</v>
+        <v>5.22</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>240.28</v>
+        <v>228.93</v>
       </c>
       <c r="W8" t="n">
-        <v>54.4</v>
+        <v>51.7</v>
       </c>
       <c r="X8" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>36.8</v>
+        <v>39.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>193.2</v>
+        <v>194.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>120.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>200.5</v>
+        <v>200.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>124.6</v>
+        <v>124.3</v>
       </c>
     </row>
     <row r="9">
@@ -1305,67 +1305,67 @@
         <v>4.824</v>
       </c>
       <c r="I9" t="n">
-        <v>441.83</v>
+        <v>442.56</v>
       </c>
       <c r="J9" t="n">
-        <v>171.82</v>
+        <v>174.77</v>
       </c>
       <c r="K9" t="n">
-        <v>38.9</v>
+        <v>39.5</v>
       </c>
       <c r="L9" t="n">
-        <v>114.66</v>
+        <v>102.56</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>88.77</v>
+        <v>102.62</v>
       </c>
       <c r="O9" t="n">
-        <v>20.1</v>
+        <v>23.2</v>
       </c>
       <c r="P9" t="n">
-        <v>41.12</v>
+        <v>47.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="R9" t="n">
-        <v>18.41</v>
+        <v>12.87</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>7.05</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="V9" t="n">
-        <v>375.25</v>
+        <v>379.95</v>
       </c>
       <c r="W9" t="n">
-        <v>84.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>90.8</v>
+        <v>91</v>
       </c>
       <c r="Y9" t="n">
-        <v>74.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="Z9" t="n">
-        <v>242.1</v>
+        <v>243.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>150.4</v>
+        <v>151.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>252.4</v>
+        <v>252</v>
       </c>
       <c r="AC9" t="n">
-        <v>156.8</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="10">
@@ -1400,37 +1400,37 @@
         <v>5.755</v>
       </c>
       <c r="I10" t="n">
-        <v>441.83</v>
+        <v>442.56</v>
       </c>
       <c r="J10" t="n">
-        <v>259.22</v>
+        <v>241.4</v>
       </c>
       <c r="K10" t="n">
-        <v>58.7</v>
+        <v>54.5</v>
       </c>
       <c r="L10" t="n">
-        <v>68.31</v>
+        <v>77.41</v>
       </c>
       <c r="M10" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="N10" t="n">
-        <v>83.97</v>
+        <v>103.9</v>
       </c>
       <c r="O10" t="n">
-        <v>19</v>
+        <v>23.5</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>10.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>16.33</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1439,28 +1439,28 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>411.5</v>
+        <v>422.71</v>
       </c>
       <c r="W10" t="n">
-        <v>93.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="X10" t="n">
-        <v>96</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>85.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>282.4</v>
+        <v>285.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>175.5</v>
+        <v>177.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>301.1</v>
+        <v>300.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>187.1</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="11">
@@ -1495,67 +1495,67 @@
         <v>3.832</v>
       </c>
       <c r="I11" t="n">
-        <v>535.17</v>
+        <v>536.02</v>
       </c>
       <c r="J11" t="n">
-        <v>77.91</v>
+        <v>38.25</v>
       </c>
       <c r="K11" t="n">
-        <v>14.6</v>
+        <v>7.1</v>
       </c>
       <c r="L11" t="n">
-        <v>66.02</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="N11" t="n">
-        <v>205.05</v>
+        <v>224.03</v>
       </c>
       <c r="O11" t="n">
-        <v>38.3</v>
+        <v>41.8</v>
       </c>
       <c r="P11" t="n">
-        <v>106.42</v>
+        <v>128.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.9</v>
+        <v>23.9</v>
       </c>
       <c r="R11" t="n">
-        <v>69.41</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="T11" t="n">
-        <v>10.36</v>
+        <v>4.66</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="V11" t="n">
-        <v>348.98</v>
+        <v>335.38</v>
       </c>
       <c r="W11" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="X11" t="n">
-        <v>83.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.1</v>
+        <v>49.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>204.1</v>
+        <v>204.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>126.8</v>
+        <v>126.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>231.3</v>
+        <v>230.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>143.7</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="12">
@@ -1590,67 +1590,67 @@
         <v>4.824</v>
       </c>
       <c r="I12" t="n">
-        <v>535.17</v>
+        <v>536.02</v>
       </c>
       <c r="J12" t="n">
-        <v>249.44</v>
+        <v>257.38</v>
       </c>
       <c r="K12" t="n">
-        <v>46.6</v>
+        <v>48</v>
       </c>
       <c r="L12" t="n">
-        <v>133.79</v>
+        <v>129.49</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="N12" t="n">
-        <v>90.84999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="O12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="P12" t="n">
-        <v>35.06</v>
+        <v>46.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>19.94</v>
+        <v>12.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>6.09</v>
+        <v>1.51</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="V12" t="n">
-        <v>474.08</v>
+        <v>475.51</v>
       </c>
       <c r="W12" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="X12" t="n">
-        <v>93.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>80.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>255.5</v>
+        <v>256.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>158.8</v>
+        <v>159.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>291.3</v>
+        <v>290.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>181</v>
+        <v>180.4</v>
       </c>
     </row>
     <row r="13">
@@ -1685,37 +1685,37 @@
         <v>5.755</v>
       </c>
       <c r="I13" t="n">
-        <v>535.17</v>
+        <v>536.02</v>
       </c>
       <c r="J13" t="n">
-        <v>351.83</v>
+        <v>337.24</v>
       </c>
       <c r="K13" t="n">
-        <v>65.7</v>
+        <v>62.9</v>
       </c>
       <c r="L13" t="n">
-        <v>81.31999999999999</v>
+        <v>100.72</v>
       </c>
       <c r="M13" t="n">
-        <v>15.2</v>
+        <v>18.8</v>
       </c>
       <c r="N13" t="n">
-        <v>72.3</v>
+        <v>79.95</v>
       </c>
       <c r="O13" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="P13" t="n">
-        <v>15.41</v>
+        <v>9.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>14.31</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1724,32 +1724,602 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>505.45</v>
+        <v>517.91</v>
       </c>
       <c r="W13" t="n">
-        <v>94.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>97.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>89</v>
+        <v>93.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>296.6</v>
+        <v>301.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>184.3</v>
+        <v>187.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>347.5</v>
+        <v>346.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>215.9</v>
+        <v>215.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TO-WDN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Voie actuelle (VIA / Transport Canada) | Current track (VIA / Transport Canada)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F14" t="n">
+        <v>76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.832</v>
+      </c>
+      <c r="I14" t="n">
+        <v>358.91</v>
+      </c>
+      <c r="J14" t="n">
+        <v>170.91</v>
+      </c>
+      <c r="K14" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>258.58</v>
+      </c>
+      <c r="W14" t="n">
+        <v>72</v>
+      </c>
+      <c r="X14" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>251</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TO-WDN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pendulaire LRC, dévers max standard CN (5 po) | LRC tilting, CN standard maximum cant (5 in)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>127</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>152</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.824</v>
+      </c>
+      <c r="I15" t="n">
+        <v>358.91</v>
+      </c>
+      <c r="J15" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="O15" t="n">
+        <v>11</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="W15" t="n">
+        <v>95</v>
+      </c>
+      <c r="X15" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>316</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>196.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TO-WDN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pendulaire moderne, insuffisance 270 mm (5 po de dévers) | Modern tilting, 270 mm cant deficiency (5 in cant)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>127</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>270</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.755</v>
+      </c>
+      <c r="I16" t="n">
+        <v>358.91</v>
+      </c>
+      <c r="J16" t="n">
+        <v>270.87</v>
+      </c>
+      <c r="K16" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>347.54</v>
+      </c>
+      <c r="W16" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>197.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>360</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>223.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Voie actuelle (VIA / Transport Canada) | Current track (VIA / Transport Canada)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F17" t="n">
+        <v>76</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.832</v>
+      </c>
+      <c r="I17" t="n">
+        <v>289.72</v>
+      </c>
+      <c r="J17" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>116.53</v>
+      </c>
+      <c r="O17" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>208.85</v>
+      </c>
+      <c r="W17" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>210.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>238.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>148.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pendulaire LRC, dévers max standard CN (5 po) | LRC tilting, CN standard maximum cant (5 in)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>127</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>152</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.824</v>
+      </c>
+      <c r="I18" t="n">
+        <v>289.72</v>
+      </c>
+      <c r="J18" t="n">
+        <v>152.78</v>
+      </c>
+      <c r="K18" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="M18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="O18" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>261.78</v>
+      </c>
+      <c r="W18" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="X18" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>186.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TO-SAR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pendulaire moderne, insuffisance 270 mm (5 po de dévers) | Modern tilting, 270 mm cant deficiency (5 in cant)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>127</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>270</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.755</v>
+      </c>
+      <c r="I19" t="n">
+        <v>289.72</v>
+      </c>
+      <c r="J19" t="n">
+        <v>208.85</v>
+      </c>
+      <c r="K19" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>268.59</v>
+      </c>
+      <c r="W19" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>307.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>358.1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>222.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC13"/>
+  <autoFilter ref="A1:AC19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/synthese_troncon.xlsx
+++ b/livrables/synthese_troncon.xlsx
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>recommande</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/livrables/synthese_troncon.xlsx
+++ b/livrables/synthese_troncon.xlsx
@@ -661,22 +661,22 @@
         <v>36.3</v>
       </c>
       <c r="P2" t="n">
-        <v>67.95</v>
+        <v>56.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.2</v>
+        <v>21.1</v>
       </c>
       <c r="R2" t="n">
-        <v>73.92</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>27.4</v>
+        <v>26.2</v>
       </c>
       <c r="T2" t="n">
-        <v>14.08</v>
+        <v>28.46</v>
       </c>
       <c r="U2" t="n">
-        <v>5.2</v>
+        <v>10.6</v>
       </c>
       <c r="V2" t="n">
         <v>113.6</v>
@@ -691,10 +691,10 @@
         <v>26.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>167.4</v>
+        <v>155.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>104</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AB2" t="n">
         <v>199.1</v>
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -750,46 +750,46 @@
         <v>24.6</v>
       </c>
       <c r="N3" t="n">
-        <v>38.52</v>
+        <v>26.31</v>
       </c>
       <c r="O3" t="n">
-        <v>14.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>34.99</v>
+        <v>25.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="R3" t="n">
-        <v>42.55</v>
+        <v>56.03</v>
       </c>
       <c r="S3" t="n">
-        <v>15.8</v>
+        <v>20.8</v>
       </c>
       <c r="T3" t="n">
-        <v>3.44</v>
+        <v>11.45</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="V3" t="n">
-        <v>188.57</v>
+        <v>176.36</v>
       </c>
       <c r="W3" t="n">
-        <v>70</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>86.90000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>56.4</v>
+        <v>35.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>210.3</v>
+        <v>195</v>
       </c>
       <c r="AA3" t="n">
-        <v>130.7</v>
+        <v>121.2</v>
       </c>
       <c r="AB3" t="n">
         <v>250.7</v>
@@ -839,52 +839,52 @@
         <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>42.89</v>
+        <v>35.11</v>
       </c>
       <c r="M4" t="n">
-        <v>15.9</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>42.14</v>
+        <v>29.79</v>
       </c>
       <c r="O4" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="P4" t="n">
-        <v>49.46</v>
+        <v>55.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.3</v>
+        <v>20.7</v>
       </c>
       <c r="R4" t="n">
-        <v>19.21</v>
+        <v>27.38</v>
       </c>
       <c r="S4" t="n">
-        <v>7.1</v>
+        <v>10.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>200.88</v>
+        <v>180.75</v>
       </c>
       <c r="W4" t="n">
-        <v>74.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="X4" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>69.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>249.3</v>
+        <v>231.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>154.9</v>
+        <v>143.7</v>
       </c>
       <c r="AB4" t="n">
         <v>299.1</v>
@@ -946,22 +946,22 @@
         <v>20.5</v>
       </c>
       <c r="P5" t="n">
-        <v>20.62</v>
+        <v>13.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.2</v>
+        <v>7.3</v>
       </c>
       <c r="R5" t="n">
-        <v>95.34999999999999</v>
+        <v>92.89</v>
       </c>
       <c r="S5" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.88</v>
+        <v>13.39</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="V5" t="n">
         <v>64.95</v>
@@ -976,16 +976,16 @@
         <v>49.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>157.7</v>
+        <v>150.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>98</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>130.4</v>
+        <v>127.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>81</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -996,7 +996,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1035,52 +1035,52 @@
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>11.21</v>
+        <v>3.06</v>
       </c>
       <c r="O6" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="P6" t="n">
-        <v>77.84999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.1</v>
+        <v>40.8</v>
       </c>
       <c r="R6" t="n">
-        <v>19.29</v>
+        <v>26.25</v>
       </c>
       <c r="S6" t="n">
-        <v>10.4</v>
+        <v>14.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>87.66</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>47.4</v>
+        <v>43</v>
       </c>
       <c r="X6" t="n">
         <v>87.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>68.8</v>
+        <v>56</v>
       </c>
       <c r="Z6" t="n">
-        <v>197.5</v>
+        <v>188.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>122.7</v>
+        <v>117.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>164.2</v>
+        <v>160.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>102</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="7">
@@ -1124,58 +1124,58 @@
         <v>35.2</v>
       </c>
       <c r="L7" t="n">
-        <v>17.51</v>
+        <v>12.63</v>
       </c>
       <c r="M7" t="n">
-        <v>9.5</v>
+        <v>6.8</v>
       </c>
       <c r="N7" t="n">
-        <v>9.609999999999999</v>
+        <v>4.17</v>
       </c>
       <c r="O7" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>83.69</v>
+        <v>86.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>45.3</v>
+        <v>46.9</v>
       </c>
       <c r="R7" t="n">
-        <v>9.02</v>
+        <v>16.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>92.09</v>
+        <v>81.77</v>
       </c>
       <c r="W7" t="n">
-        <v>49.8</v>
+        <v>44.2</v>
       </c>
       <c r="X7" t="n">
         <v>92.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>75.2</v>
+        <v>58.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>233.1</v>
+        <v>222.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>144.8</v>
+        <v>138.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>195.9</v>
+        <v>191.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>121.7</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="8">
@@ -1231,22 +1231,22 @@
         <v>28.9</v>
       </c>
       <c r="P8" t="n">
-        <v>115.19</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R8" t="n">
-        <v>93.22</v>
+        <v>116.25</v>
       </c>
       <c r="S8" t="n">
-        <v>21.1</v>
+        <v>26.3</v>
       </c>
       <c r="T8" t="n">
-        <v>5.22</v>
+        <v>17.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
         <v>228.93</v>
@@ -1261,10 +1261,10 @@
         <v>39.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>194.5</v>
+        <v>180.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>120.9</v>
+        <v>111.9</v>
       </c>
       <c r="AB8" t="n">
         <v>200.1</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1320,46 +1320,46 @@
         <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>102.62</v>
+        <v>60.87</v>
       </c>
       <c r="O9" t="n">
-        <v>23.2</v>
+        <v>13.8</v>
       </c>
       <c r="P9" t="n">
-        <v>47.28</v>
+        <v>36.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>12.87</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>14.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.46</v>
+        <v>3.51</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="V9" t="n">
-        <v>379.95</v>
+        <v>338.2</v>
       </c>
       <c r="W9" t="n">
-        <v>85.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="X9" t="n">
         <v>91</v>
       </c>
       <c r="Y9" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="Z9" t="n">
-        <v>243.8</v>
+        <v>225.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>151.5</v>
+        <v>140.3</v>
       </c>
       <c r="AB9" t="n">
         <v>252</v>
@@ -1409,52 +1409,52 @@
         <v>54.5</v>
       </c>
       <c r="L10" t="n">
-        <v>77.41</v>
+        <v>53.59</v>
       </c>
       <c r="M10" t="n">
-        <v>17.5</v>
+        <v>12.1</v>
       </c>
       <c r="N10" t="n">
-        <v>103.9</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>23.5</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>10.81</v>
+        <v>48.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>9.039999999999999</v>
+        <v>20.07</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="n">
-        <v>422.71</v>
+        <v>370.14</v>
       </c>
       <c r="W10" t="n">
-        <v>95.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="X10" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>91.2</v>
+        <v>56.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>285.3</v>
+        <v>264.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>177.3</v>
+        <v>164.4</v>
       </c>
       <c r="AB10" t="n">
         <v>300.6</v>
@@ -1516,22 +1516,22 @@
         <v>41.8</v>
       </c>
       <c r="P11" t="n">
-        <v>128.19</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.9</v>
+        <v>16.6</v>
       </c>
       <c r="R11" t="n">
-        <v>67.79000000000001</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>12.6</v>
+        <v>17.9</v>
       </c>
       <c r="T11" t="n">
-        <v>4.66</v>
+        <v>15.64</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="V11" t="n">
         <v>335.38</v>
@@ -1546,10 +1546,10 @@
         <v>49.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>204.3</v>
+        <v>191.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>126.9</v>
+        <v>119.1</v>
       </c>
       <c r="AB11" t="n">
         <v>230.7</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1605,46 +1605,46 @@
         <v>24.2</v>
       </c>
       <c r="N12" t="n">
-        <v>88.64</v>
+        <v>43.93</v>
       </c>
       <c r="O12" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>46.64</v>
+        <v>35.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="R12" t="n">
-        <v>12.36</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.51</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="V12" t="n">
-        <v>475.51</v>
+        <v>430.8</v>
       </c>
       <c r="W12" t="n">
-        <v>88.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>85.59999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>256.3</v>
+        <v>240.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>159.3</v>
+        <v>149.4</v>
       </c>
       <c r="AB12" t="n">
         <v>290.4</v>
@@ -1694,52 +1694,52 @@
         <v>62.9</v>
       </c>
       <c r="L13" t="n">
-        <v>100.72</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>79.95</v>
+        <v>50.29</v>
       </c>
       <c r="O13" t="n">
-        <v>14.9</v>
+        <v>9.4</v>
       </c>
       <c r="P13" t="n">
-        <v>9.98</v>
+        <v>53.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="R13" t="n">
-        <v>8.130000000000001</v>
+        <v>19.59</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>517.91</v>
+        <v>462.82</v>
       </c>
       <c r="W13" t="n">
-        <v>96.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="X13" t="n">
         <v>97.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>93.8</v>
+        <v>61.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>301.1</v>
+        <v>282.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>187.1</v>
+        <v>175.7</v>
       </c>
       <c r="AB13" t="n">
         <v>346.5</v>
@@ -1801,22 +1801,22 @@
         <v>18.5</v>
       </c>
       <c r="P14" t="n">
-        <v>58.01</v>
+        <v>47.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.2</v>
+        <v>13.4</v>
       </c>
       <c r="R14" t="n">
-        <v>39.63</v>
+        <v>43.34</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>12.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="V14" t="n">
         <v>258.58</v>
@@ -1831,10 +1831,10 @@
         <v>44.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>233.3</v>
+        <v>224.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>145</v>
+        <v>139.7</v>
       </c>
       <c r="AB14" t="n">
         <v>251</v>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1890,46 +1890,46 @@
         <v>18.2</v>
       </c>
       <c r="N15" t="n">
-        <v>39.38</v>
+        <v>29.05</v>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="P15" t="n">
-        <v>11.8</v>
+        <v>7.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>6.23</v>
+        <v>18.89</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V15" t="n">
-        <v>340.88</v>
+        <v>330.55</v>
       </c>
       <c r="W15" t="n">
-        <v>95</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="X15" t="n">
         <v>96.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>80.5</v>
+        <v>61</v>
       </c>
       <c r="Z15" t="n">
-        <v>286.1</v>
+        <v>276.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>177.8</v>
+        <v>171.6</v>
       </c>
       <c r="AB15" t="n">
         <v>316</v>
@@ -1979,52 +1979,52 @@
         <v>75.5</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45</v>
+        <v>34.62</v>
       </c>
       <c r="M16" t="n">
-        <v>12.1</v>
+        <v>9.6</v>
       </c>
       <c r="N16" t="n">
-        <v>33.22</v>
+        <v>27.02</v>
       </c>
       <c r="O16" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="P16" t="n">
-        <v>8.68</v>
+        <v>16.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.69</v>
+        <v>9.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V16" t="n">
-        <v>347.54</v>
+        <v>332.51</v>
       </c>
       <c r="W16" t="n">
-        <v>96.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>89.8</v>
+        <v>63.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>317.2</v>
+        <v>306.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>197.1</v>
+        <v>190.7</v>
       </c>
       <c r="AB16" t="n">
         <v>360</v>
@@ -2086,22 +2086,22 @@
         <v>40.2</v>
       </c>
       <c r="P17" t="n">
-        <v>34.97</v>
+        <v>20.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.1</v>
+        <v>7.2</v>
       </c>
       <c r="R17" t="n">
-        <v>45.84</v>
+        <v>53.6</v>
       </c>
       <c r="S17" t="n">
-        <v>15.8</v>
+        <v>18.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06</v>
+        <v>6.41</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
         <v>208.85</v>
@@ -2116,10 +2116,10 @@
         <v>44.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>210.3</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="n">
-        <v>130.7</v>
+        <v>124.9</v>
       </c>
       <c r="AB17" t="n">
         <v>238.4</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>recommande</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2175,46 +2175,46 @@
         <v>23.4</v>
       </c>
       <c r="N18" t="n">
-        <v>41.13</v>
+        <v>26.68</v>
       </c>
       <c r="O18" t="n">
-        <v>14.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>23.75</v>
+        <v>18.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="R18" t="n">
-        <v>4.19</v>
+        <v>23.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="V18" t="n">
-        <v>261.78</v>
+        <v>247.33</v>
       </c>
       <c r="W18" t="n">
-        <v>90.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="X18" t="n">
         <v>97.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>80.90000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>263.6</v>
+        <v>252</v>
       </c>
       <c r="AA18" t="n">
-        <v>163.8</v>
+        <v>156.6</v>
       </c>
       <c r="AB18" t="n">
         <v>300.2</v>
@@ -2264,28 +2264,28 @@
         <v>72.09999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>29.52</v>
+        <v>19.01</v>
       </c>
       <c r="M19" t="n">
-        <v>10.2</v>
+        <v>6.6</v>
       </c>
       <c r="N19" t="n">
-        <v>30.22</v>
+        <v>21.54</v>
       </c>
       <c r="O19" t="n">
-        <v>10.4</v>
+        <v>7.4</v>
       </c>
       <c r="P19" t="n">
-        <v>20.44</v>
+        <v>33.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.1</v>
+        <v>11.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2294,22 +2294,22 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>268.59</v>
+        <v>249.4</v>
       </c>
       <c r="W19" t="n">
-        <v>92.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>99</v>
       </c>
       <c r="Y19" t="n">
-        <v>90.40000000000001</v>
+        <v>57.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>307.2</v>
+        <v>293.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>190.9</v>
+        <v>182.6</v>
       </c>
       <c r="AB19" t="n">
         <v>358.1</v>
